--- a/库存表.xlsx
+++ b/库存表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="库存台账" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="库存台账" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -506,6 +506,14 @@
       <c r="F2" s="2" t="n">
         <v>25.5</v>
       </c>
+      <c r="G2" s="2">
+        <f>D2*F2</f>
+        <v/>
+      </c>
+      <c r="H2" s="2">
+        <f>IF(D2&gt;E2,"过多",IF(D2&lt;E2,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -532,6 +540,14 @@
       <c r="F3" s="2" t="n">
         <v>2.5</v>
       </c>
+      <c r="G3" s="2">
+        <f>D3*F3</f>
+        <v/>
+      </c>
+      <c r="H3" s="2">
+        <f>IF(D3&gt;E3,"过多",IF(D3&lt;E3,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -558,6 +574,14 @@
       <c r="F4" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="G4" s="2">
+        <f>D4*F4</f>
+        <v/>
+      </c>
+      <c r="H4" s="2">
+        <f>IF(D4&gt;E4,"过多",IF(D4&lt;E4,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -584,6 +608,14 @@
       <c r="F5" s="2" t="n">
         <v>480</v>
       </c>
+      <c r="G5" s="2">
+        <f>D5*F5</f>
+        <v/>
+      </c>
+      <c r="H5" s="2">
+        <f>IF(D5&gt;E5,"过多",IF(D5&lt;E5,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,6 +642,14 @@
       <c r="F6" s="2" t="n">
         <v>89</v>
       </c>
+      <c r="G6" s="2">
+        <f>D6*F6</f>
+        <v/>
+      </c>
+      <c r="H6" s="2">
+        <f>IF(D6&gt;E6,"过多",IF(D6&lt;E6,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,6 +676,14 @@
       <c r="F7" s="2" t="n">
         <v>59</v>
       </c>
+      <c r="G7" s="2">
+        <f>D7*F7</f>
+        <v/>
+      </c>
+      <c r="H7" s="2">
+        <f>IF(D7&gt;E7,"过多",IF(D7&lt;E7,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -662,6 +710,14 @@
       <c r="F8" s="2" t="n">
         <v>329</v>
       </c>
+      <c r="G8" s="2">
+        <f>D8*F8</f>
+        <v/>
+      </c>
+      <c r="H8" s="2">
+        <f>IF(D8&gt;E8,"过多",IF(D8&lt;E8,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -688,6 +744,14 @@
       <c r="F9" s="2" t="n">
         <v>1099</v>
       </c>
+      <c r="G9" s="2">
+        <f>D9*F9</f>
+        <v/>
+      </c>
+      <c r="H9" s="2">
+        <f>IF(D9&gt;E9,"过多",IF(D9&lt;E9,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -714,6 +778,14 @@
       <c r="F10" s="2" t="n">
         <v>129</v>
       </c>
+      <c r="G10" s="2">
+        <f>D10*F10</f>
+        <v/>
+      </c>
+      <c r="H10" s="2">
+        <f>IF(D10&gt;E10,"过多",IF(D10&lt;E10,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -740,6 +812,14 @@
       <c r="F11" s="2" t="n">
         <v>159</v>
       </c>
+      <c r="G11" s="2">
+        <f>D11*F11</f>
+        <v/>
+      </c>
+      <c r="H11" s="2">
+        <f>IF(D11&gt;E11,"过多",IF(D11&lt;E11,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -766,6 +846,14 @@
       <c r="F12" s="2" t="n">
         <v>349</v>
       </c>
+      <c r="G12" s="2">
+        <f>D12*F12</f>
+        <v/>
+      </c>
+      <c r="H12" s="2">
+        <f>IF(D12&gt;E12,"过多",IF(D12&lt;E12,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -792,6 +880,14 @@
       <c r="F13" s="2" t="n">
         <v>42</v>
       </c>
+      <c r="G13" s="2">
+        <f>D13*F13</f>
+        <v/>
+      </c>
+      <c r="H13" s="2">
+        <f>IF(D13&gt;E13,"过多",IF(D13&lt;E13,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -818,6 +914,14 @@
       <c r="F14" s="2" t="n">
         <v>68</v>
       </c>
+      <c r="G14" s="2">
+        <f>D14*F14</f>
+        <v/>
+      </c>
+      <c r="H14" s="2">
+        <f>IF(D14&gt;E14,"过多",IF(D14&lt;E14,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -844,6 +948,14 @@
       <c r="F15" s="2" t="n">
         <v>12.5</v>
       </c>
+      <c r="G15" s="2">
+        <f>D15*F15</f>
+        <v/>
+      </c>
+      <c r="H15" s="2">
+        <f>IF(D15&gt;E15,"过多",IF(D15&lt;E15,"需补货","正常"))</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -869,6 +981,14 @@
       </c>
       <c r="F16" s="2" t="n">
         <v>6.8</v>
+      </c>
+      <c r="G16" s="2">
+        <f>D16*F16</f>
+        <v/>
+      </c>
+      <c r="H16" s="2">
+        <f>IF(D16&gt;E16,"过多",IF(D16&lt;E16,"需补货","正常"))</f>
+        <v/>
       </c>
     </row>
     <row r="18">
